--- a/劉怡伶/HW0927/HW 0927.xlsx
+++ b/劉怡伶/HW0927/HW 0927.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b9361\Desktop\在職\統計學\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF9F44F-D31C-42BA-97EC-A9DD43ED07FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A3D6F8-8247-41EE-B0BB-065573723095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FAF24491-FACC-47A3-91A1-021646E0C0B6}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="殘差" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="127">
   <si>
     <t>Cell Phone</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -105,10 +106,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">a. dependent variable : temp </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>XY</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -133,19 +130,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>-7.638=y-2.026x</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>least-sqr line</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>-7.638=27-2.026x</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>x=</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -165,10 +150,6 @@
   </si>
   <si>
     <t xml:space="preserve">    independent variable : Floors</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">    independent variable : chirps</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -404,14 +385,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>a.0.4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>b. 0.05*3*4=0.6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>CH04.02_Q29</t>
   </si>
   <si>
@@ -436,15 +409,118 @@
   <si>
     <t>No Preschool</t>
   </si>
+  <si>
+    <t xml:space="preserve">    independent variable : temp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>a. dependent variable : Chirps</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.115=y-0.405x</t>
+  </si>
+  <si>
+    <t>6.115=y-0.405x</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>摘要輸出</t>
+  </si>
+  <si>
+    <t>迴歸統計</t>
+  </si>
+  <si>
+    <t>R 的倍數</t>
+  </si>
+  <si>
+    <t>R 平方</t>
+  </si>
+  <si>
+    <t>調整的 R 平方</t>
+  </si>
+  <si>
+    <t>標準誤</t>
+  </si>
+  <si>
+    <t>觀察值個數</t>
+  </si>
+  <si>
+    <t>ANOVA</t>
+  </si>
+  <si>
+    <t>迴歸</t>
+  </si>
+  <si>
+    <t>殘差</t>
+  </si>
+  <si>
+    <t>總和</t>
+  </si>
+  <si>
+    <t>截距</t>
+  </si>
+  <si>
+    <t>自由度</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>顯著值</t>
+  </si>
+  <si>
+    <t>係數</t>
+  </si>
+  <si>
+    <t>t 統計</t>
+  </si>
+  <si>
+    <t>P-值</t>
+  </si>
+  <si>
+    <t>下限 95%</t>
+  </si>
+  <si>
+    <t>上限 95%</t>
+  </si>
+  <si>
+    <t>下限 95.0%</t>
+  </si>
+  <si>
+    <t>上限 95.0%</t>
+  </si>
+  <si>
+    <t>Floors</t>
+  </si>
+  <si>
+    <t>殘差輸出</t>
+  </si>
+  <si>
+    <t>觀察值</t>
+  </si>
+  <si>
+    <t>預測為 Height</t>
+  </si>
+  <si>
+    <t>=3/20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="181" formatCode="0.000"/>
-    <numFmt numFmtId="182" formatCode="0.0"/>
-    <numFmt numFmtId="208" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -526,7 +602,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -551,14 +627,8 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -599,6 +669,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -608,7 +698,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -636,35 +726,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="208" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1261,7 +1360,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="zh-TW"/>
+          <a:endParaRPr lang="en-US" altLang="zh-TW"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1892,6 +1991,7 @@
         <c:axId val="1547698848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="20"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1954,6 +2054,7 @@
         <c:axId val="1547690208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="13"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -8412,13 +8513,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>552449</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>25401</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>177801</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12423,7 +12524,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="I25" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="N25" t="s">
         <v>8</v>
@@ -12437,10 +12538,10 @@
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.4">
@@ -12506,14 +12607,14 @@
         <v>504</v>
       </c>
       <c r="N31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O31">
         <f>(G37-N33)/9</f>
         <v>6.9555555555555957</v>
       </c>
       <c r="P31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q31">
         <f>O31/E39/F39</f>
@@ -12532,18 +12633,18 @@
         <v>384</v>
       </c>
       <c r="N32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O32" s="9">
-        <f>Q31*E39/F39</f>
-        <v>2.0258899676375464</v>
+        <f>Q31*F39/E39</f>
+        <v>0.40544041450777529</v>
       </c>
       <c r="P32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q32" s="9">
-        <f>E38-(O32*F38)</f>
-        <v>-7.6375404530745286</v>
+        <f>F38-(O32*E38)</f>
+        <v>6.115284974093175</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.4">
@@ -12562,10 +12663,10 @@
         <v>4495.3999999999996</v>
       </c>
       <c r="P33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q33" s="8" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.4">
@@ -12619,17 +12720,17 @@
         <v>4558</v>
       </c>
       <c r="N37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O37" s="8" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="Q37" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R37" s="11">
-        <f>27-Q32/O32</f>
-        <v>30.769968051118248</v>
+        <f>6.115+0.405*27</f>
+        <v>17.05</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.4">
@@ -12655,21 +12756,21 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.4">
       <c r="G44" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H44" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.4">
@@ -12684,7 +12785,7 @@
         <v>24455</v>
       </c>
       <c r="L45" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.4">
@@ -12786,7 +12887,7 @@
         <v>11388</v>
       </c>
       <c r="L53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M53" s="10">
         <f>(I73-K55)/27</f>
@@ -12881,7 +12982,7 @@
         <v>9120</v>
       </c>
       <c r="L60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M60" s="12">
         <f>M53/I75</f>
@@ -12900,7 +13001,7 @@
         <v>7938</v>
       </c>
       <c r="M61" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="7:13" x14ac:dyDescent="0.4">
@@ -13049,10 +13150,10 @@
         <v>290252</v>
       </c>
       <c r="L73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M73" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N73">
         <f>M60*G75/H75</f>
@@ -13070,7 +13171,7 @@
       </c>
       <c r="I74" s="7"/>
       <c r="M74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N74">
         <f>G74-(N73*H74)</f>
@@ -13091,12 +13192,12 @@
         <v>414.86157454301127</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="7:14" x14ac:dyDescent="0.4">
       <c r="L76" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M76" s="11">
         <f>4.4*48-13.91</f>
@@ -13115,231 +13216,228 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A85" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.4">
       <c r="J88" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.4">
       <c r="G89" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J89" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.4">
       <c r="J90" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D91" t="s">
+        <v>34</v>
+      </c>
+      <c r="G91" t="s">
         <v>39</v>
       </c>
-      <c r="G91" t="s">
-        <v>44</v>
-      </c>
       <c r="J91" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.4">
       <c r="J92" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B93" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G93" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J93" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D94" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J94" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G95" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J95" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D97" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G97" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J97" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B98" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J98" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.4">
       <c r="G99" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J99" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D100" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J100" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.4">
       <c r="G101" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J101" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.4">
       <c r="J102" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.4">
       <c r="G103" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J103" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.4">
       <c r="J104" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A107" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B113" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C113" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D113" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E113" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F113" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B114" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C114" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D114" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E114" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F114" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B115" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C115" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D115" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E115" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F115" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A119" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.4">
       <c r="G125" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H125">
         <f>1/20</f>
         <v>0.05</v>
       </c>
-      <c r="J125" t="s">
-        <v>92</v>
+      <c r="J125" s="8" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.4">
       <c r="G126" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H126">
         <f t="shared" ref="H126:H144" si="4">1/20</f>
         <v>0.05</v>
       </c>
-      <c r="J126" t="s">
-        <v>93</v>
-      </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.4">
       <c r="G127" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H127">
         <f t="shared" si="4"/>
@@ -13348,16 +13446,16 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.4">
       <c r="G128" t="s">
-        <v>90</v>
-      </c>
-      <c r="H128" s="16">
+        <v>85</v>
+      </c>
+      <c r="H128">
         <f t="shared" si="4"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="129" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G129" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H129">
         <f t="shared" si="4"/>
@@ -13366,7 +13464,7 @@
     </row>
     <row r="130" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G130" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H130">
         <f t="shared" si="4"/>
@@ -13375,7 +13473,7 @@
     </row>
     <row r="131" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G131" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H131">
         <f t="shared" si="4"/>
@@ -13384,16 +13482,16 @@
     </row>
     <row r="132" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G132" t="s">
-        <v>90</v>
-      </c>
-      <c r="H132" s="16">
+        <v>85</v>
+      </c>
+      <c r="H132">
         <f t="shared" si="4"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="133" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G133" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H133">
         <f t="shared" si="4"/>
@@ -13402,7 +13500,7 @@
     </row>
     <row r="134" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G134" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H134">
         <f t="shared" si="4"/>
@@ -13411,7 +13509,7 @@
     </row>
     <row r="135" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G135" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H135">
         <f t="shared" si="4"/>
@@ -13420,16 +13518,16 @@
     </row>
     <row r="136" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G136" t="s">
-        <v>90</v>
-      </c>
-      <c r="H136" s="16">
+        <v>85</v>
+      </c>
+      <c r="H136">
         <f t="shared" si="4"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="137" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G137" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H137">
         <f t="shared" si="4"/>
@@ -13438,7 +13536,7 @@
     </row>
     <row r="138" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G138" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H138">
         <f t="shared" si="4"/>
@@ -13447,7 +13545,7 @@
     </row>
     <row r="139" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G139" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H139">
         <f t="shared" si="4"/>
@@ -13456,52 +13554,52 @@
     </row>
     <row r="140" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G140" t="s">
-        <v>90</v>
-      </c>
-      <c r="H140" s="16">
+        <v>85</v>
+      </c>
+      <c r="H140">
         <f t="shared" si="4"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="141" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G141" t="s">
-        <v>91</v>
-      </c>
-      <c r="H141" s="16">
+        <v>86</v>
+      </c>
+      <c r="H141">
         <f t="shared" si="4"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="142" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G142" t="s">
-        <v>87</v>
-      </c>
-      <c r="H142" s="16">
+        <v>82</v>
+      </c>
+      <c r="H142">
         <f t="shared" si="4"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="143" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G143" t="s">
-        <v>88</v>
-      </c>
-      <c r="H143" s="16">
+        <v>83</v>
+      </c>
+      <c r="H143">
         <f t="shared" si="4"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="144" spans="7:8" x14ac:dyDescent="0.4">
       <c r="G144" t="s">
-        <v>89</v>
-      </c>
-      <c r="H144" s="16">
+        <v>84</v>
+      </c>
+      <c r="H144">
         <f t="shared" si="4"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A145" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.4">
@@ -13514,57 +13612,57 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.4">
       <c r="G160" s="13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H160" s="13" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="I160" s="13" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.4">
       <c r="D161" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G161" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="H161" s="17">
+        <v>92</v>
+      </c>
+      <c r="H161" s="16">
         <f>8/14</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="I161" s="17">
+      <c r="I161" s="16">
         <f>9/11</f>
         <v>0.81818181818181823</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.4">
       <c r="G162" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="H162" s="18">
+        <v>93</v>
+      </c>
+      <c r="H162" s="17">
         <f>1-H161</f>
         <v>0.4285714285714286</v>
       </c>
-      <c r="I162" s="18">
+      <c r="I162" s="17">
         <f>1-I161</f>
         <v>0.18181818181818177</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B163" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.4">
       <c r="D164" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.4">
@@ -13578,17 +13676,17 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.4">
       <c r="D167" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B168" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.4">
       <c r="G169" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H169">
         <f>(1-H166)*I162</f>
@@ -13597,7 +13695,7 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.4">
       <c r="D170" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -13608,4 +13706,551 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92AA0D11-8B8B-4893-A438-AAFA8D8D80B8}">
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="21"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="18">
+        <v>0.95657584408415242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A5" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="18">
+        <v>0.91503734548530857</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="18">
+        <v>0.9117695510808973</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="18">
+        <v>12.982214637373097</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="19">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A12" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="18">
+        <v>1</v>
+      </c>
+      <c r="C12" s="18">
+        <v>47193.443252267134</v>
+      </c>
+      <c r="D12" s="18">
+        <v>47193.443252267134</v>
+      </c>
+      <c r="E12" s="18">
+        <v>280.01680407130135</v>
+      </c>
+      <c r="F12" s="18">
+        <v>1.9413091399991482E-15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A13" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="18">
+        <v>26</v>
+      </c>
+      <c r="C13" s="18">
+        <v>4381.985319161432</v>
+      </c>
+      <c r="D13" s="18">
+        <v>168.5378968908243</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="19">
+        <v>27</v>
+      </c>
+      <c r="C14" s="19">
+        <v>51575.428571428565</v>
+      </c>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="18">
+        <v>-13.906512419989497</v>
+      </c>
+      <c r="C17" s="18">
+        <v>13.184005666377328</v>
+      </c>
+      <c r="D17" s="18">
+        <v>-1.0548017629766917</v>
+      </c>
+      <c r="E17" s="18">
+        <v>0.30121973943427038</v>
+      </c>
+      <c r="F17" s="18">
+        <v>-41.006624186462545</v>
+      </c>
+      <c r="G17" s="18">
+        <v>13.193599346483548</v>
+      </c>
+      <c r="H17" s="18">
+        <v>-41.006624186462545</v>
+      </c>
+      <c r="I17" s="18">
+        <v>13.193599346483548</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="19">
+        <v>4.4044864642668404</v>
+      </c>
+      <c r="C18" s="19">
+        <v>0.26321051346539737</v>
+      </c>
+      <c r="D18" s="19">
+        <v>16.733702640817462</v>
+      </c>
+      <c r="E18" s="19">
+        <v>1.9413091399991482E-15</v>
+      </c>
+      <c r="F18" s="19">
+        <v>3.8634495052784099</v>
+      </c>
+      <c r="G18" s="19">
+        <v>4.9455234232552714</v>
+      </c>
+      <c r="H18" s="19">
+        <v>3.8634495052784099</v>
+      </c>
+      <c r="I18" s="19">
+        <v>4.9455234232552714</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" s="18">
+        <v>1</v>
+      </c>
+      <c r="B25" s="18">
+        <v>307.62099947148988</v>
+      </c>
+      <c r="C25" s="18">
+        <v>27.379000528510119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" s="18">
+        <v>2</v>
+      </c>
+      <c r="B26" s="18">
+        <v>307.62099947148988</v>
+      </c>
+      <c r="C26" s="18">
+        <v>2.3790005285101188</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" s="18">
+        <v>3</v>
+      </c>
+      <c r="B27" s="18">
+        <v>259.17164836455458</v>
+      </c>
+      <c r="C27" s="18">
+        <v>2.828351635445415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28" s="18">
+        <v>4</v>
+      </c>
+      <c r="B28" s="18">
+        <v>215.1267837218862</v>
+      </c>
+      <c r="C28" s="18">
+        <v>13.873216278113802</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29" s="18">
+        <v>5</v>
+      </c>
+      <c r="B29" s="18">
+        <v>215.1267837218862</v>
+      </c>
+      <c r="C29" s="18">
+        <v>12.873216278113802</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A30" s="18">
+        <v>6</v>
+      </c>
+      <c r="B30" s="18">
+        <v>228.34024311468673</v>
+      </c>
+      <c r="C30" s="18">
+        <v>-4.3402431146867286</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A31" s="18">
+        <v>7</v>
+      </c>
+      <c r="B31" s="18">
+        <v>219.53127018615305</v>
+      </c>
+      <c r="C31" s="18">
+        <v>1.4687298138469487</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A32" s="18">
+        <v>8</v>
+      </c>
+      <c r="B32" s="18">
+        <v>223.93575665041988</v>
+      </c>
+      <c r="C32" s="18">
+        <v>-3.9357566504198758</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="18">
+        <v>9</v>
+      </c>
+      <c r="B33" s="18">
+        <v>215.1267837218862</v>
+      </c>
+      <c r="C33" s="18">
+        <v>3.8732162781138015</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="18">
+        <v>10</v>
+      </c>
+      <c r="B34" s="18">
+        <v>215.1267837218862</v>
+      </c>
+      <c r="C34" s="18">
+        <v>-2.1267837218861985</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="18">
+        <v>11</v>
+      </c>
+      <c r="B35" s="18">
+        <v>215.1267837218862</v>
+      </c>
+      <c r="C35" s="18">
+        <v>-2.1267837218861985</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="18">
+        <v>12</v>
+      </c>
+      <c r="B36" s="18">
+        <v>201.9133243290857</v>
+      </c>
+      <c r="C36" s="18">
+        <v>4.0866756709143033</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="18">
+        <v>13</v>
+      </c>
+      <c r="B37" s="18">
+        <v>223.93575665041988</v>
+      </c>
+      <c r="C37" s="18">
+        <v>-20.935756650419876</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="18">
+        <v>14</v>
+      </c>
+      <c r="B38" s="18">
+        <v>241.55370250748726</v>
+      </c>
+      <c r="C38" s="18">
+        <v>-44.553702507487259</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="18">
+        <v>15</v>
+      </c>
+      <c r="B39" s="18">
+        <v>201.9133243290857</v>
+      </c>
+      <c r="C39" s="18">
+        <v>-7.9133243290856967</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" s="18">
+        <v>16</v>
+      </c>
+      <c r="B40" s="18">
+        <v>197.50883786481884</v>
+      </c>
+      <c r="C40" s="18">
+        <v>-7.5088378648188439</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="18">
+        <v>17</v>
+      </c>
+      <c r="B41" s="18">
+        <v>171.08191907921781</v>
+      </c>
+      <c r="C41" s="18">
+        <v>17.918080920782188</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="18">
+        <v>18</v>
+      </c>
+      <c r="B42" s="18">
+        <v>184.29537847201831</v>
+      </c>
+      <c r="C42" s="18">
+        <v>0.70462152798168631</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A43" s="18">
+        <v>19</v>
+      </c>
+      <c r="B43" s="18">
+        <v>171.08191907921781</v>
+      </c>
+      <c r="C43" s="18">
+        <v>4.9180809207821881</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A44" s="18">
+        <v>20</v>
+      </c>
+      <c r="B44" s="18">
+        <v>179.89089200775149</v>
+      </c>
+      <c r="C44" s="18">
+        <v>-5.8908920077514892</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45" s="18">
+        <v>21</v>
+      </c>
+      <c r="B45" s="18">
+        <v>179.89089200775149</v>
+      </c>
+      <c r="C45" s="18">
+        <v>-5.8908920077514892</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A46" s="18">
+        <v>22</v>
+      </c>
+      <c r="B46" s="18">
+        <v>166.67743261495096</v>
+      </c>
+      <c r="C46" s="18">
+        <v>-3.6774326149509591</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" s="18">
+        <v>23</v>
+      </c>
+      <c r="B47" s="18">
+        <v>157.86845968641728</v>
+      </c>
+      <c r="C47" s="18">
+        <v>4.1315403135827182</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48" s="18">
+        <v>24</v>
+      </c>
+      <c r="B48" s="18">
+        <v>162.27294615068411</v>
+      </c>
+      <c r="C48" s="18">
+        <v>-0.27294615068410621</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A49" s="18">
+        <v>25</v>
+      </c>
+      <c r="B49" s="18">
+        <v>162.27294615068411</v>
+      </c>
+      <c r="C49" s="18">
+        <v>-0.27294615068410621</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50" s="18">
+        <v>26</v>
+      </c>
+      <c r="B50" s="18">
+        <v>149.0594867578836</v>
+      </c>
+      <c r="C50" s="18">
+        <v>8.9405132421163955</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" s="18">
+        <v>27</v>
+      </c>
+      <c r="B51" s="18">
+        <v>162.27294615068411</v>
+      </c>
+      <c r="C51" s="18">
+        <v>-5.2729461506841062</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="19">
+        <v>28</v>
+      </c>
+      <c r="B52" s="19">
+        <v>144.65500029361675</v>
+      </c>
+      <c r="C52" s="19">
+        <v>9.3449997063832484</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/劉怡伶/HW0927/HW 0927.xlsx
+++ b/劉怡伶/HW0927/HW 0927.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\b9361\Desktop\在職\統計學\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A3D6F8-8247-41EE-B0BB-065573723095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE985EA-8233-41CC-B4A6-E30D61CE143D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FAF24491-FACC-47A3-91A1-021646E0C0B6}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="128">
   <si>
     <t>Cell Phone</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -512,6 +512,10 @@
     <t>=3/20</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>Z Score</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -602,7 +606,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -625,6 +629,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -753,17 +763,17 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12769,6 +12779,9 @@
       <c r="I44" t="s">
         <v>15</v>
       </c>
+      <c r="J44" t="s">
+        <v>127</v>
+      </c>
       <c r="L44" t="s">
         <v>25</v>
       </c>
@@ -12784,6 +12797,10 @@
         <f>G45*H45</f>
         <v>24455</v>
       </c>
+      <c r="J45" s="21">
+        <f>(G45-G$74)/G$75</f>
+        <v>3.0234594761159097</v>
+      </c>
       <c r="L45" t="s">
         <v>26</v>
       </c>
@@ -12799,6 +12816,10 @@
         <f t="shared" ref="I46:I72" si="2">G46*H46</f>
         <v>22630</v>
       </c>
+      <c r="J46" s="10">
+        <f t="shared" ref="J46:J72" si="3">(G46-G$74)/G$75</f>
+        <v>2.4514536292831699</v>
+      </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.4">
       <c r="G47">
@@ -12811,6 +12832,10 @@
         <f t="shared" si="2"/>
         <v>16244</v>
       </c>
+      <c r="J47" s="10">
+        <f t="shared" si="3"/>
+        <v>1.3532024033643097</v>
+      </c>
       <c r="L47" t="s">
         <v>5</v>
       </c>
@@ -12826,6 +12851,10 @@
         <f t="shared" si="2"/>
         <v>11908</v>
       </c>
+      <c r="J48" s="10">
+        <f t="shared" si="3"/>
+        <v>0.59815468554509343</v>
+      </c>
     </row>
     <row r="49" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G49">
@@ -12838,6 +12867,10 @@
         <f t="shared" si="2"/>
         <v>11856</v>
       </c>
+      <c r="J49" s="10">
+        <f t="shared" si="3"/>
+        <v>0.57527445167178382</v>
+      </c>
     </row>
     <row r="50" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G50">
@@ -12850,6 +12883,10 @@
         <f t="shared" si="2"/>
         <v>12320</v>
       </c>
+      <c r="J50" s="10">
+        <f t="shared" si="3"/>
+        <v>0.48375351617854551</v>
+      </c>
     </row>
     <row r="51" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G51">
@@ -12862,6 +12899,10 @@
         <f t="shared" si="2"/>
         <v>11713</v>
       </c>
+      <c r="J51" s="10">
+        <f t="shared" si="3"/>
+        <v>0.41511281455861671</v>
+      </c>
     </row>
     <row r="52" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G52">
@@ -12874,6 +12915,10 @@
         <f t="shared" si="2"/>
         <v>11880</v>
       </c>
+      <c r="J52" s="10">
+        <f t="shared" si="3"/>
+        <v>0.39223258068530714</v>
+      </c>
     </row>
     <row r="53" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G53">
@@ -12886,6 +12931,10 @@
         <f t="shared" si="2"/>
         <v>11388</v>
       </c>
+      <c r="J53" s="10">
+        <f t="shared" si="3"/>
+        <v>0.36935234681199752</v>
+      </c>
       <c r="L53" t="s">
         <v>16</v>
       </c>
@@ -12905,6 +12954,10 @@
         <f t="shared" si="2"/>
         <v>11076</v>
       </c>
+      <c r="J54" s="10">
+        <f t="shared" si="3"/>
+        <v>0.23207094357214</v>
+      </c>
     </row>
     <row r="55" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G55">
@@ -12917,6 +12970,10 @@
         <f t="shared" si="2"/>
         <v>11076</v>
       </c>
+      <c r="J55" s="10">
+        <f t="shared" si="3"/>
+        <v>0.23207094357214</v>
+      </c>
       <c r="K55">
         <f>G73*H73/28</f>
         <v>279537.14285714284</v>
@@ -12933,6 +12990,10 @@
         <f t="shared" si="2"/>
         <v>10094</v>
       </c>
+      <c r="J56" s="10">
+        <f t="shared" si="3"/>
+        <v>7.1909306458972894E-2</v>
+      </c>
     </row>
     <row r="57" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G57">
@@ -12945,6 +13006,10 @@
         <f t="shared" si="2"/>
         <v>10962</v>
       </c>
+      <c r="J57" s="10">
+        <f t="shared" si="3"/>
+        <v>3.2686048390441341E-3</v>
+      </c>
     </row>
     <row r="58" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G58">
@@ -12957,6 +13022,10 @@
         <f t="shared" si="2"/>
         <v>11426</v>
       </c>
+      <c r="J58" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.1340127984008134</v>
+      </c>
     </row>
     <row r="59" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G59">
@@ -12969,6 +13038,10 @@
         <f t="shared" si="2"/>
         <v>9506</v>
       </c>
+      <c r="J59" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.20265350002074217</v>
+      </c>
     </row>
     <row r="60" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G60">
@@ -12981,6 +13054,10 @@
         <f t="shared" si="2"/>
         <v>9120</v>
       </c>
+      <c r="J60" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.29417443551398054</v>
+      </c>
       <c r="L60" t="s">
         <v>18</v>
       </c>
@@ -13000,6 +13077,10 @@
         <f t="shared" si="2"/>
         <v>7938</v>
       </c>
+      <c r="J61" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.3170546693872901</v>
+      </c>
       <c r="M61" t="s">
         <v>27</v>
       </c>
@@ -13015,6 +13096,10 @@
         <f t="shared" si="2"/>
         <v>8325</v>
       </c>
+      <c r="J62" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.40857560488052846</v>
+      </c>
     </row>
     <row r="63" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G63">
@@ -13027,6 +13112,10 @@
         <f t="shared" si="2"/>
         <v>7392</v>
       </c>
+      <c r="J63" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.6144977097403147</v>
+      </c>
     </row>
     <row r="64" spans="7:13" x14ac:dyDescent="0.4">
       <c r="G64">
@@ -13039,6 +13128,10 @@
         <f t="shared" si="2"/>
         <v>7656</v>
       </c>
+      <c r="J64" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.66025817748693394</v>
+      </c>
     </row>
     <row r="65" spans="7:14" x14ac:dyDescent="0.4">
       <c r="G65">
@@ -13051,6 +13144,10 @@
         <f t="shared" si="2"/>
         <v>7656</v>
       </c>
+      <c r="J65" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.66025817748693394</v>
+      </c>
     </row>
     <row r="66" spans="7:14" x14ac:dyDescent="0.4">
       <c r="G66">
@@ -13063,6 +13160,10 @@
         <f t="shared" si="2"/>
         <v>6683</v>
       </c>
+      <c r="J66" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.91194075009333941</v>
+      </c>
     </row>
     <row r="67" spans="7:14" x14ac:dyDescent="0.4">
       <c r="G67">
@@ -13075,6 +13176,10 @@
         <f t="shared" si="2"/>
         <v>6318</v>
       </c>
+      <c r="J67" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.93482098396664903</v>
+      </c>
     </row>
     <row r="68" spans="7:14" x14ac:dyDescent="0.4">
       <c r="G68">
@@ -13087,6 +13192,10 @@
         <f t="shared" si="2"/>
         <v>6480</v>
       </c>
+      <c r="J68" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.93482098396664903</v>
+      </c>
     </row>
     <row r="69" spans="7:14" x14ac:dyDescent="0.4">
       <c r="G69">
@@ -13099,6 +13208,10 @@
         <f t="shared" si="2"/>
         <v>6480</v>
       </c>
+      <c r="J69" s="10">
+        <f t="shared" si="3"/>
+        <v>-0.93482098396664903</v>
+      </c>
     </row>
     <row r="70" spans="7:14" x14ac:dyDescent="0.4">
       <c r="G70">
@@ -13111,6 +13224,10 @@
         <f t="shared" si="2"/>
         <v>5846</v>
       </c>
+      <c r="J70" s="10">
+        <f t="shared" si="3"/>
+        <v>-1.0263419194598873</v>
+      </c>
     </row>
     <row r="71" spans="7:14" x14ac:dyDescent="0.4">
       <c r="G71">
@@ -13123,6 +13240,10 @@
         <f t="shared" si="2"/>
         <v>6280</v>
       </c>
+      <c r="J71" s="10">
+        <f t="shared" si="3"/>
+        <v>-1.0492221533331969</v>
+      </c>
     </row>
     <row r="72" spans="7:14" x14ac:dyDescent="0.4">
       <c r="G72">
@@ -13134,6 +13255,10 @@
       <c r="I72">
         <f t="shared" si="2"/>
         <v>5544</v>
+      </c>
+      <c r="J72" s="10">
+        <f t="shared" si="3"/>
+        <v>-1.1178628549531258</v>
       </c>
     </row>
     <row r="73" spans="7:14" x14ac:dyDescent="0.4">
@@ -13142,11 +13267,11 @@
         <v>5680</v>
       </c>
       <c r="H73" s="7">
-        <f t="shared" ref="H73:I73" si="3">SUM(H45:H72)</f>
+        <f t="shared" ref="H73:I73" si="4">SUM(H45:H72)</f>
         <v>1378</v>
       </c>
       <c r="I73" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>290252</v>
       </c>
       <c r="L73" t="s">
@@ -13431,7 +13556,7 @@
         <v>83</v>
       </c>
       <c r="H126">
-        <f t="shared" ref="H126:H144" si="4">1/20</f>
+        <f t="shared" ref="H126:H144" si="5">1/20</f>
         <v>0.05</v>
       </c>
     </row>
@@ -13440,7 +13565,7 @@
         <v>84</v>
       </c>
       <c r="H127">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13449,7 +13574,7 @@
         <v>85</v>
       </c>
       <c r="H128">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13458,7 +13583,7 @@
         <v>86</v>
       </c>
       <c r="H129">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13467,7 +13592,7 @@
         <v>83</v>
       </c>
       <c r="H130">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13476,7 +13601,7 @@
         <v>84</v>
       </c>
       <c r="H131">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13485,7 +13610,7 @@
         <v>85</v>
       </c>
       <c r="H132">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13494,7 +13619,7 @@
         <v>86</v>
       </c>
       <c r="H133">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13503,7 +13628,7 @@
         <v>82</v>
       </c>
       <c r="H134">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13512,7 +13637,7 @@
         <v>84</v>
       </c>
       <c r="H135">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13521,7 +13646,7 @@
         <v>85</v>
       </c>
       <c r="H136">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13530,7 +13655,7 @@
         <v>86</v>
       </c>
       <c r="H137">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13539,7 +13664,7 @@
         <v>82</v>
       </c>
       <c r="H138">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13548,7 +13673,7 @@
         <v>83</v>
       </c>
       <c r="H139">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13557,7 +13682,7 @@
         <v>85</v>
       </c>
       <c r="H140">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13566,7 +13691,7 @@
         <v>86</v>
       </c>
       <c r="H141">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13575,7 +13700,7 @@
         <v>82</v>
       </c>
       <c r="H142">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13584,7 +13709,7 @@
         <v>83</v>
       </c>
       <c r="H143">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13593,7 +13718,7 @@
         <v>84</v>
       </c>
       <c r="H144">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.05</v>
       </c>
     </row>
@@ -13720,48 +13845,48 @@
     </row>
     <row r="2" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="B3" s="21"/>
+      <c r="B3" s="20"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="18" t="s">
+      <c r="A4" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4">
         <v>0.95657584408415242</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
+      <c r="A5" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5">
         <v>0.91503734548530857</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="18" t="s">
+      <c r="A6" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6">
         <v>0.9117695510808973</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="18" t="s">
+      <c r="A7" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7">
         <v>12.982214637373097</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <v>28</v>
       </c>
     </row>
@@ -13771,156 +13896,154 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="19" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="18" t="s">
+      <c r="A12" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12">
         <v>47193.443252267134</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12">
         <v>47193.443252267134</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12">
         <v>280.01680407130135</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12">
         <v>1.9413091399991482E-15</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="18" t="s">
+      <c r="A13" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13">
         <v>26</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13">
         <v>4381.985319161432</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13">
         <v>168.5378968908243</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <v>27</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <v>51575.428571428565</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
     </row>
     <row r="15" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20" t="s">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="I16" s="20" t="s">
+      <c r="I16" s="19" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="18" t="s">
+      <c r="A17" t="s">
         <v>109</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17">
         <v>-13.906512419989497</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17">
         <v>13.184005666377328</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17">
         <v>-1.0548017629766917</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17">
         <v>0.30121973943427038</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17">
         <v>-41.006624186462545</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17">
         <v>13.193599346483548</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17">
         <v>-41.006624186462545</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17">
         <v>13.193599346483548</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="18">
         <v>4.4044864642668404</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="18">
         <v>0.26321051346539737</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="18">
         <v>16.733702640817462</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="18">
         <v>1.9413091399991482E-15</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="18">
         <v>3.8634495052784099</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="18">
         <v>4.9455234232552714</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="18">
         <v>3.8634495052784099</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="18">
         <v>4.9455234232552714</v>
       </c>
     </row>
@@ -13931,321 +14054,520 @@
     </row>
     <row r="23" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="19" t="s">
         <v>107</v>
       </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="18">
+      <c r="A25">
         <v>1</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25">
         <v>307.62099947148988</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25">
         <v>27.379000528510119</v>
       </c>
+      <c r="D25">
+        <v>335</v>
+      </c>
+      <c r="E25">
+        <f>D25-B25</f>
+        <v>27.379000528510119</v>
+      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="18">
+      <c r="A26">
         <v>2</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26">
         <v>307.62099947148988</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26">
         <v>2.3790005285101188</v>
       </c>
+      <c r="D26">
+        <v>310</v>
+      </c>
+      <c r="E26">
+        <f t="shared" ref="E26:E52" si="0">D26-B26</f>
+        <v>2.3790005285101188</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="18">
+      <c r="A27">
         <v>3</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27">
         <v>259.17164836455458</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27">
         <v>2.828351635445415</v>
       </c>
+      <c r="D27">
+        <v>262</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="0"/>
+        <v>2.828351635445415</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="18">
+      <c r="A28">
         <v>4</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28">
         <v>215.1267837218862</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28">
         <v>13.873216278113802</v>
       </c>
+      <c r="D28">
+        <v>229</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="0"/>
+        <v>13.873216278113802</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="18">
+      <c r="A29">
         <v>5</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29">
         <v>215.1267837218862</v>
       </c>
-      <c r="C29" s="18">
+      <c r="C29">
         <v>12.873216278113802</v>
       </c>
+      <c r="D29">
+        <v>228</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="0"/>
+        <v>12.873216278113802</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="18">
+      <c r="A30">
         <v>6</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30">
         <v>228.34024311468673</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30">
         <v>-4.3402431146867286</v>
       </c>
+      <c r="D30">
+        <v>224</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="0"/>
+        <v>-4.3402431146867286</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="18">
+      <c r="A31">
         <v>7</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31">
         <v>219.53127018615305</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31">
         <v>1.4687298138469487</v>
       </c>
+      <c r="D31">
+        <v>221</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="0"/>
+        <v>1.4687298138469487</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="18">
+      <c r="A32">
         <v>8</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32">
         <v>223.93575665041988</v>
       </c>
-      <c r="C32" s="18">
+      <c r="C32">
         <v>-3.9357566504198758</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A33" s="18">
+      <c r="D32">
+        <v>220</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="0"/>
+        <v>-3.9357566504198758</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33">
         <v>9</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33">
         <v>215.1267837218862</v>
       </c>
-      <c r="C33" s="18">
+      <c r="C33">
         <v>3.8732162781138015</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34" s="18">
+      <c r="D33">
+        <v>219</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="0"/>
+        <v>3.8732162781138015</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34">
         <v>10</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34">
         <v>215.1267837218862</v>
       </c>
-      <c r="C34" s="18">
+      <c r="C34">
         <v>-2.1267837218861985</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A35" s="18">
+      <c r="D34">
+        <v>213</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="0"/>
+        <v>-2.1267837218861985</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35">
         <v>11</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35">
         <v>215.1267837218862</v>
       </c>
-      <c r="C35" s="18">
+      <c r="C35">
         <v>-2.1267837218861985</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A36" s="18">
+      <c r="D35">
+        <v>213</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="0"/>
+        <v>-2.1267837218861985</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36">
         <v>12</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36">
         <v>201.9133243290857</v>
       </c>
-      <c r="C36" s="18">
+      <c r="C36">
         <v>4.0866756709143033</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A37" s="18">
+      <c r="D36">
+        <v>206</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="0"/>
+        <v>4.0866756709143033</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37">
         <v>13</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37">
         <v>223.93575665041988</v>
       </c>
-      <c r="C37" s="18">
+      <c r="C37">
         <v>-20.935756650419876</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38" s="18">
+      <c r="D37">
+        <v>203</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="0"/>
+        <v>-20.935756650419876</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A38">
         <v>14</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38">
         <v>241.55370250748726</v>
       </c>
-      <c r="C38" s="18">
+      <c r="C38">
         <v>-44.553702507487259</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A39" s="18">
+      <c r="D38">
+        <v>197</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="0"/>
+        <v>-44.553702507487259</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A39">
         <v>15</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39">
         <v>201.9133243290857</v>
       </c>
-      <c r="C39" s="18">
+      <c r="C39">
         <v>-7.9133243290856967</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A40" s="18">
+      <c r="D39">
+        <v>194</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="0"/>
+        <v>-7.9133243290856967</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A40">
         <v>16</v>
       </c>
-      <c r="B40" s="18">
+      <c r="B40">
         <v>197.50883786481884</v>
       </c>
-      <c r="C40" s="18">
+      <c r="C40">
         <v>-7.5088378648188439</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A41" s="18">
+      <c r="D40">
+        <v>190</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="0"/>
+        <v>-7.5088378648188439</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A41">
         <v>17</v>
       </c>
-      <c r="B41" s="18">
+      <c r="B41">
         <v>171.08191907921781</v>
       </c>
-      <c r="C41" s="18">
+      <c r="C41">
         <v>17.918080920782188</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A42" s="18">
+      <c r="D41">
+        <v>189</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="0"/>
+        <v>17.918080920782188</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A42">
         <v>18</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42">
         <v>184.29537847201831</v>
       </c>
-      <c r="C42" s="18">
+      <c r="C42">
         <v>0.70462152798168631</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A43" s="18">
+      <c r="D42">
+        <v>185</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="0"/>
+        <v>0.70462152798168631</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A43">
         <v>19</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43">
         <v>171.08191907921781</v>
       </c>
-      <c r="C43" s="18">
+      <c r="C43">
         <v>4.9180809207821881</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A44" s="18">
+      <c r="D43">
+        <v>176</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="0"/>
+        <v>4.9180809207821881</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A44">
         <v>20</v>
       </c>
-      <c r="B44" s="18">
+      <c r="B44">
         <v>179.89089200775149</v>
       </c>
-      <c r="C44" s="18">
+      <c r="C44">
         <v>-5.8908920077514892</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A45" s="18">
+      <c r="D44">
+        <v>174</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="0"/>
+        <v>-5.8908920077514892</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A45">
         <v>21</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45">
         <v>179.89089200775149</v>
       </c>
-      <c r="C45" s="18">
+      <c r="C45">
         <v>-5.8908920077514892</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A46" s="18">
+      <c r="D45">
+        <v>174</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="0"/>
+        <v>-5.8908920077514892</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A46">
         <v>22</v>
       </c>
-      <c r="B46" s="18">
+      <c r="B46">
         <v>166.67743261495096</v>
       </c>
-      <c r="C46" s="18">
+      <c r="C46">
         <v>-3.6774326149509591</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A47" s="18">
+      <c r="D46">
+        <v>163</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="0"/>
+        <v>-3.6774326149509591</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A47">
         <v>23</v>
       </c>
-      <c r="B47" s="18">
+      <c r="B47">
         <v>157.86845968641728</v>
       </c>
-      <c r="C47" s="18">
+      <c r="C47">
         <v>4.1315403135827182</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A48" s="18">
+      <c r="D47">
+        <v>162</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="0"/>
+        <v>4.1315403135827182</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A48">
         <v>24</v>
       </c>
-      <c r="B48" s="18">
+      <c r="B48">
         <v>162.27294615068411</v>
       </c>
-      <c r="C48" s="18">
+      <c r="C48">
         <v>-0.27294615068410621</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A49" s="18">
+      <c r="D48">
+        <v>162</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="0"/>
+        <v>-0.27294615068410621</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A49">
         <v>25</v>
       </c>
-      <c r="B49" s="18">
+      <c r="B49">
         <v>162.27294615068411</v>
       </c>
-      <c r="C49" s="18">
+      <c r="C49">
         <v>-0.27294615068410621</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A50" s="18">
+      <c r="D49">
+        <v>162</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="0"/>
+        <v>-0.27294615068410621</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A50">
         <v>26</v>
       </c>
-      <c r="B50" s="18">
+      <c r="B50">
         <v>149.0594867578836</v>
       </c>
-      <c r="C50" s="18">
+      <c r="C50">
         <v>8.9405132421163955</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A51" s="18">
+      <c r="D50">
+        <v>158</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="0"/>
+        <v>8.9405132421163955</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A51">
         <v>27</v>
       </c>
-      <c r="B51" s="18">
+      <c r="B51">
         <v>162.27294615068411</v>
       </c>
-      <c r="C51" s="18">
+      <c r="C51">
         <v>-5.2729461506841062</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="19">
+      <c r="D51">
+        <v>157</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="0"/>
+        <v>-5.2729461506841062</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="18">
         <v>28</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="18">
         <v>144.65500029361675</v>
       </c>
-      <c r="C52" s="19">
+      <c r="C52" s="18">
+        <v>9.3449997063832484</v>
+      </c>
+      <c r="D52">
+        <v>154</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="0"/>
         <v>9.3449997063832484</v>
       </c>
     </row>
